--- a/hira_material_automation/output/monthly/202601_202605__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>4836</t>
@@ -519,7 +523,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>4479</t>
@@ -552,7 +560,11 @@
           <t>040028</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1회용 관절 봉합용 NEEDLE(분리형)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>4556</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:07:14</t>
+          <t>2026-05-14T22:15:28</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>59af23dec801cb0b65dab7ec22a961eb78c8f065bffe594d5d6372e1379687fe</t>
+          <t>642c4a9cdc223819190ab31c35391fd67637f520501639c0fa3e020c4210c9a3</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:15:28</t>
+          <t>2026-05-24T22:00:09</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>642c4a9cdc223819190ab31c35391fd67637f520501639c0fa3e020c4210c9a3</t>
+          <t>0a7182dd3a4bb7d8a736c3daa5594631d0cd234692ef1696d25bef0e538aa867</t>
         </is>
       </c>
     </row>
